--- a/database/数据库.xlsx
+++ b/database/数据库.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Minghao Lin\IdeaProjects\coursework3\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D9CC37-CC1A-43DC-8992-9F99D9609599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D9917A4-A83D-432B-9FEB-B51C7F9845A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="270" yWindow="4095" windowWidth="25350" windowHeight="11250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -440,10 +440,6 @@
     <t>变更时间</t>
   </si>
   <si>
-    <t>booking_history表(选做)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">外键引用 </t>
     </r>
@@ -529,6 +525,10 @@
   </si>
   <si>
     <t>币种</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>booking_history表</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -612,16 +612,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -908,25 +908,25 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:17" ht="23.25">
-      <c r="A1" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
+      <c r="A1" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="3"/>
     </row>
     <row r="2" spans="1:17">
       <c r="A2" t="s">
@@ -981,10 +981,10 @@
       </c>
     </row>
     <row r="4" spans="1:17">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="6"/>
+      <c r="B4" s="4"/>
       <c r="C4" t="s">
         <v>3</v>
       </c>
@@ -1008,24 +1008,24 @@
       </c>
     </row>
     <row r="6" spans="1:17" ht="23.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
     </row>
     <row r="7" spans="1:17">
       <c r="A7" t="s">
@@ -1074,10 +1074,10 @@
       </c>
     </row>
     <row r="9" spans="1:17">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="6"/>
+      <c r="B9" s="4"/>
       <c r="C9" t="s">
         <v>32</v>
       </c>
@@ -1103,25 +1103,25 @@
       </c>
     </row>
     <row r="12" spans="1:17" ht="23.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="H12" s="5" t="s">
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="H12" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
-      <c r="K12" s="5"/>
-      <c r="L12" s="5"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="5"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3"/>
     </row>
     <row r="13" spans="1:17">
       <c r="A13" t="s">
@@ -1193,29 +1193,29 @@
       </c>
     </row>
     <row r="16" spans="1:17">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
     </row>
     <row r="18" spans="1:22" ht="23.25">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" t="s">
@@ -1240,19 +1240,19 @@
         <v>18</v>
       </c>
       <c r="N19" t="s">
+        <v>93</v>
+      </c>
+      <c r="P19" t="s">
         <v>94</v>
       </c>
-      <c r="P19" t="s">
-        <v>95</v>
-      </c>
       <c r="R19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="T19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="V19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -1281,23 +1281,23 @@
         <v>34</v>
       </c>
       <c r="P20" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="T20" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="V20" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:22">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="6"/>
+      <c r="B21" s="4"/>
       <c r="C21" s="2" t="s">
         <v>67</v>
       </c>
@@ -1317,33 +1317,33 @@
         <v>19</v>
       </c>
       <c r="N21" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="V21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="23.25">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
     </row>
     <row r="25" spans="1:22">
       <c r="A25" t="s">
@@ -1398,10 +1398,10 @@
       </c>
     </row>
     <row r="27" spans="1:22">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B27" s="6"/>
+      <c r="B27" s="4"/>
       <c r="C27" s="2" t="s">
         <v>69</v>
       </c>
@@ -1435,29 +1435,29 @@
       </c>
     </row>
     <row r="31" spans="1:22" ht="23.25">
-      <c r="A31" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="L31" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="M31" s="5"/>
-      <c r="N31" s="5"/>
-      <c r="O31" s="5"/>
-      <c r="P31" s="5"/>
-      <c r="Q31" s="5"/>
-      <c r="R31" s="5"/>
-      <c r="S31" s="5"/>
-      <c r="T31" s="5"/>
-      <c r="U31" s="5"/>
+      <c r="A31" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="L31" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="3"/>
+      <c r="S31" s="3"/>
+      <c r="T31" s="3"/>
+      <c r="U31" s="3"/>
     </row>
     <row r="32" spans="1:22">
       <c r="A32" t="s">
@@ -1482,13 +1482,13 @@
         <v>40</v>
       </c>
       <c r="Q32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S32" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U32" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:21">
@@ -1514,22 +1514,22 @@
         <v>21</v>
       </c>
       <c r="Q33" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S33" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="U33" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:21">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="6"/>
+      <c r="B34" s="4"/>
       <c r="C34" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E34" t="s">
         <v>72</v>
@@ -1540,21 +1540,21 @@
       <c r="G34" t="s">
         <v>76</v>
       </c>
-      <c r="L34" s="6" t="s">
+      <c r="L34" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="6"/>
+      <c r="M34" s="4"/>
       <c r="N34" s="2" t="s">
         <v>67</v>
       </c>
       <c r="Q34" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S34" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U34" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:21">
@@ -1565,10 +1565,10 @@
         <v>18</v>
       </c>
       <c r="P36" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="R36" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T36" cm="1">
         <f t="array" aca="1" ref="T36" ca="1">A1:T36</f>
@@ -1583,7 +1583,7 @@
         <v>16</v>
       </c>
       <c r="P37" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="R37" t="s">
         <v>26</v>
@@ -1597,14 +1597,21 @@
         <v>62</v>
       </c>
       <c r="P38" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="R38" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="H12:P12"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A6:P6"/>
+    <mergeCell ref="A12:F12"/>
     <mergeCell ref="A31:I31"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="A21:B21"/>
@@ -1613,13 +1620,6 @@
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="L34:M34"/>
     <mergeCell ref="L31:U31"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="H12:P12"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A6:P6"/>
-    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
